--- a/training_survey_templates/024_corporate_virtual_training_feedback_questionnaire--training_survey_templates.xlsx
+++ b/training_survey_templates/024_corporate_virtual_training_feedback_questionnaire--training_survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'session_1',_'value':_'session_1'}</t>
+          <t>session_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Session 1', 'value': 'Session 1'}</t>
+          <t>Session 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'session_2',_'value':_'session_2'}</t>
+          <t>session_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Session 2', 'value': 'Session 2'}</t>
+          <t>Session 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'department_1'}</t>
+          <t>department_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Department 1'}</t>
+          <t>Department 1</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'department_2'}</t>
+          <t>department_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Department 2'}</t>
+          <t>Department 2</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'user_1',_'value':_'user_1'}</t>
+          <t>user_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'User 1', 'value': 'User 1'}</t>
+          <t>User 1</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'user_2',_'value':_'user_2'}</t>
+          <t>user_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'User 2', 'value': 'User 2'}</t>
+          <t>User 2</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'user_3',_'value':_'user_3'}</t>
+          <t>user_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'User 3', 'value': 'User 3'}</t>
+          <t>User 3</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'department_1',_'value':_'department_1'}</t>
+          <t>department_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Department 1', 'value': 'Department 1'}</t>
+          <t>Department 1</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'department_2',_'value':_'department_2'}</t>
+          <t>department_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Department 2', 'value': 'Department 2'}</t>
+          <t>Department 2</t>
         </is>
       </c>
     </row>
